--- a/02_실전캠프_Day2_실습제출/3조_강상구_숯불에닭/v1/프로젝트/public/sample/가짜_거래내역_2026-08.xlsx
+++ b/02_실전캠프_Day2_실습제출/3조_강상구_숯불에닭/v1/프로젝트/public/sample/가짜_거래내역_2026-08.xlsx
@@ -1910,10 +1910,10 @@
         <v/>
       </c>
       <c r="E68">
-        <v>1600000</v>
+        <v>1220000</v>
       </c>
       <c r="F68">
-        <v>6621000</v>
+        <v>6241000</v>
       </c>
       <c r="G68" t="str">
         <v>가짜지점</v>
@@ -1936,7 +1936,7 @@
         <v/>
       </c>
       <c r="F69">
-        <v>6556000</v>
+        <v>6176000</v>
       </c>
       <c r="G69" t="str">
         <v>가짜지점</v>
@@ -1956,10 +1956,10 @@
         <v/>
       </c>
       <c r="E70">
-        <v>430000</v>
+        <v>310000</v>
       </c>
       <c r="F70">
-        <v>6986000</v>
+        <v>6486000</v>
       </c>
       <c r="G70" t="str">
         <v>가짜지점</v>
@@ -1982,7 +1982,7 @@
         <v/>
       </c>
       <c r="F71">
-        <v>6736000</v>
+        <v>6236000</v>
       </c>
       <c r="G71" t="str">
         <v>가짜지점</v>
@@ -2005,7 +2005,7 @@
         <v/>
       </c>
       <c r="F72">
-        <v>6703000</v>
+        <v>6203000</v>
       </c>
       <c r="G72" t="str">
         <v>가짜지점</v>
@@ -2025,10 +2025,10 @@
         <v/>
       </c>
       <c r="E73">
-        <v>1950000</v>
+        <v>1500000</v>
       </c>
       <c r="F73">
-        <v>8653000</v>
+        <v>7703000</v>
       </c>
       <c r="G73" t="str">
         <v>가짜지점</v>
@@ -2051,7 +2051,7 @@
         <v/>
       </c>
       <c r="F74">
-        <v>8596000</v>
+        <v>7646000</v>
       </c>
       <c r="G74" t="str">
         <v>가짜지점</v>
@@ -2071,10 +2071,10 @@
         <v/>
       </c>
       <c r="E75">
-        <v>1020000</v>
+        <v>720000</v>
       </c>
       <c r="F75">
-        <v>9616000</v>
+        <v>8366000</v>
       </c>
       <c r="G75" t="str">
         <v>가짜지점</v>
@@ -2097,7 +2097,7 @@
         <v/>
       </c>
       <c r="F76">
-        <v>9516000</v>
+        <v>8266000</v>
       </c>
       <c r="G76" t="str">
         <v>가짜지점</v>
@@ -2120,7 +2120,7 @@
         <v>470000</v>
       </c>
       <c r="F77">
-        <v>9986000</v>
+        <v>8736000</v>
       </c>
       <c r="G77" t="str">
         <v>가짜지점</v>
@@ -2143,7 +2143,7 @@
         <v/>
       </c>
       <c r="F78">
-        <v>9890000</v>
+        <v>8640000</v>
       </c>
       <c r="G78" t="str">
         <v>가짜지점</v>
